--- a/diseases/d064/2015-2019.xlsx
+++ b/diseases/d064/2015-2019.xlsx
@@ -905,9 +905,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1293,9 +1290,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -2157,9 +2151,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -3021,9 +3012,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3885,9 +3873,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4893,9 +4878,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -5757,9 +5739,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -6621,9 +6600,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -7629,9 +7605,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -8493,9 +8466,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -9357,9 +9327,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -10365,9 +10332,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -11229,9 +11193,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -12093,9 +12054,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -12625,9 +12583,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -13489,9 +13444,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -14353,9 +14305,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -15361,9 +15310,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -16225,9 +16171,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -17089,9 +17032,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -18097,9 +18037,6 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
@@ -18961,9 +18898,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -19825,9 +19759,6 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
@@ -20833,9 +20764,6 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
@@ -21697,9 +21625,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -22561,9 +22486,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -23569,9 +23491,6 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0</v>
       </c>
@@ -23957,9 +23876,6 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
@@ -24821,9 +24737,6 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0</v>
       </c>
@@ -25685,9 +25598,6 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
@@ -26693,9 +26603,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -27557,9 +27464,6 @@
       <c r="O186" t="n">
         <v>0</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0</v>
       </c>
@@ -28421,9 +28325,6 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0</v>
       </c>
@@ -29429,9 +29330,6 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0</v>
       </c>
@@ -30293,9 +30191,6 @@
       <c r="O205" t="n">
         <v>0</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0</v>
       </c>
@@ -31301,9 +31196,6 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0</v>
       </c>
@@ -32165,9 +32057,6 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -33029,9 +32918,6 @@
       <c r="O224" t="n">
         <v>0</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0</v>
       </c>
@@ -34037,9 +33923,6 @@
       <c r="O231" t="n">
         <v>0</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0</v>
       </c>
@@ -34901,9 +34784,6 @@
       <c r="O237" t="n">
         <v>0</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>0</v>
       </c>
@@ -35289,9 +35169,6 @@
       <c r="O239" t="n">
         <v>0</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0</v>
       </c>
@@ -36153,9 +36030,6 @@
       <c r="O245" t="n">
         <v>0</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0</v>
       </c>
@@ -37017,9 +36891,6 @@
       <c r="O251" t="n">
         <v>0</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0</v>
       </c>
@@ -38025,9 +37896,6 @@
       <c r="O258" t="n">
         <v>0</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="R258" t="n">
         <v>0</v>
       </c>
@@ -38889,9 +38757,6 @@
       <c r="O264" t="n">
         <v>0</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="R264" t="n">
         <v>0</v>
       </c>
@@ -39897,9 +39762,6 @@
       <c r="O271" t="n">
         <v>0</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>0</v>
       </c>
@@ -40761,9 +40623,6 @@
       <c r="O277" t="n">
         <v>0</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>0</v>
       </c>
@@ -41625,9 +41484,6 @@
       <c r="O283" t="n">
         <v>0</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0</v>
       </c>
@@ -42633,9 +42489,6 @@
       <c r="O290" t="n">
         <v>0</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0</v>
       </c>
@@ -43497,9 +43350,6 @@
       <c r="O296" t="n">
         <v>0</v>
       </c>
-      <c r="Q296" t="n">
-        <v>0</v>
-      </c>
       <c r="R296" t="n">
         <v>0</v>
       </c>
@@ -44361,9 +44211,6 @@
       <c r="O302" t="n">
         <v>0</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>0</v>
       </c>
@@ -45369,9 +45216,6 @@
       <c r="O309" t="n">
         <v>0</v>
       </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
       <c r="R309" t="n">
         <v>0</v>
       </c>
@@ -46233,9 +46077,6 @@
       <c r="O315" t="n">
         <v>0</v>
       </c>
-      <c r="Q315" t="n">
-        <v>0</v>
-      </c>
       <c r="R315" t="n">
         <v>0</v>
       </c>
@@ -46621,9 +46462,6 @@
       <c r="O317" t="n">
         <v>0</v>
       </c>
-      <c r="Q317" t="n">
-        <v>0</v>
-      </c>
       <c r="R317" t="n">
         <v>0</v>
       </c>
@@ -47629,9 +47467,6 @@
       <c r="O324" t="n">
         <v>0</v>
       </c>
-      <c r="Q324" t="n">
-        <v>0</v>
-      </c>
       <c r="R324" t="n">
         <v>0</v>
       </c>
@@ -48493,9 +48328,6 @@
       <c r="O330" t="n">
         <v>0</v>
       </c>
-      <c r="Q330" t="n">
-        <v>0</v>
-      </c>
       <c r="R330" t="n">
         <v>0</v>
       </c>
@@ -49357,9 +49189,6 @@
       <c r="O336" t="n">
         <v>0</v>
       </c>
-      <c r="Q336" t="n">
-        <v>0</v>
-      </c>
       <c r="R336" t="n">
         <v>0</v>
       </c>
@@ -50221,9 +50050,6 @@
       <c r="O342" t="n">
         <v>0</v>
       </c>
-      <c r="Q342" t="n">
-        <v>0</v>
-      </c>
       <c r="R342" t="n">
         <v>0</v>
       </c>
@@ -51229,9 +51055,6 @@
       <c r="O349" t="n">
         <v>0</v>
       </c>
-      <c r="Q349" t="n">
-        <v>0</v>
-      </c>
       <c r="R349" t="n">
         <v>0</v>
       </c>
@@ -52093,9 +51916,6 @@
       <c r="O355" t="n">
         <v>0</v>
       </c>
-      <c r="Q355" t="n">
-        <v>0</v>
-      </c>
       <c r="R355" t="n">
         <v>0</v>
       </c>
@@ -52957,9 +52777,6 @@
       <c r="O361" t="n">
         <v>0</v>
       </c>
-      <c r="Q361" t="n">
-        <v>0</v>
-      </c>
       <c r="R361" t="n">
         <v>0</v>
       </c>
@@ -53965,9 +53782,6 @@
       <c r="O368" t="n">
         <v>0</v>
       </c>
-      <c r="Q368" t="n">
-        <v>0</v>
-      </c>
       <c r="R368" t="n">
         <v>0</v>
       </c>
@@ -54829,9 +54643,6 @@
       <c r="O374" t="n">
         <v>0</v>
       </c>
-      <c r="Q374" t="n">
-        <v>0</v>
-      </c>
       <c r="R374" t="n">
         <v>0</v>
       </c>
@@ -55837,9 +55648,6 @@
       <c r="O381" t="n">
         <v>0</v>
       </c>
-      <c r="Q381" t="n">
-        <v>0</v>
-      </c>
       <c r="R381" t="n">
         <v>0</v>
       </c>
@@ -56699,9 +56507,6 @@
         <v>0</v>
       </c>
       <c r="O387" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q387" t="n">
         <v>0</v>
       </c>
       <c r="R387" t="n">
